--- a/PccuClub/Template/評鑑類別維護_template.xlsx
+++ b/PccuClub/Template/評鑑類別維護_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pccu\SourceCode\SRC2\PccuClub\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079568F0-73F0-4DAA-BA14-75D869DC0450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE64ED9-62B8-42F6-89C8-0DA658E086F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>學年度</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -36,6 +36,14 @@
   </si>
   <si>
     <t>類別名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分數上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分數下限</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -390,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,6 +414,12 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
